--- a/测试集/泛用性验收_v3/W6/W6_预期_月度汇总.xlsx
+++ b/测试集/泛用性验收_v3/W6/W6_预期_月度汇总.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3月汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,28 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>责任单位</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>月份</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -446,26 +446,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>C001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>年度审计</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>财务部</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3月</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>系统上线</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>工程技术部</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>安全培训</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>市场推广</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>市场营销部</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/测试集/泛用性验收_v3/W6/W6_预期_月度汇总.xlsx
+++ b/测试集/泛用性验收_v3/W6/W6_预期_月度汇总.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +52,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +442,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>责任单位</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
@@ -496,51 +521,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>安全培训</t>
+          <t>市场推广</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>安全管理部</t>
+          <t>市场营销部</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C004</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>市场推广</t>
+          <t>安全培训</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>市场营销部</t>
+          <t>安全管理部</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
